--- a/datos/CFPB_datos_por_banda_FICO.xlsx
+++ b/datos/CFPB_datos_por_banda_FICO.xlsx
@@ -416,6 +416,17 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -476,10 +487,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.88</v>
+        <v>0.8806</v>
       </c>
       <c r="D2" t="n">
-        <v>2400</v>
+        <v>2112</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
@@ -488,14 +499,14 @@
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>25.75</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -511,26 +522,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.88</v>
+        <v>0.8339</v>
       </c>
       <c r="D3" t="n">
-        <v>2200</v>
+        <v>2057</v>
       </c>
       <c r="E3" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>30.93</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -546,26 +557,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.83</v>
+        <v>0.8168</v>
       </c>
       <c r="D4" t="n">
-        <v>2000</v>
+        <v>2230</v>
       </c>
       <c r="E4" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="F4" t="n">
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>29.42</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>12.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -581,26 +592,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.79</v>
+        <v>0.7217</v>
       </c>
       <c r="D5" t="n">
         <v>2885</v>
       </c>
       <c r="E5" t="n">
-        <v>27.3</v>
+        <v>28.96</v>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>22.65</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -616,26 +627,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.42</v>
+        <v>0.4186</v>
       </c>
       <c r="D6" t="n">
-        <v>1500</v>
+        <v>2044</v>
       </c>
       <c r="E6" t="n">
-        <v>25.8</v>
+        <v>27.72</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>10.39</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>39.52</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -651,26 +662,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2</v>
+        <v>0.1964</v>
       </c>
       <c r="D7" t="n">
         <v>874</v>
       </c>
       <c r="E7" t="n">
-        <v>22.6</v>
+        <v>25.83</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.53</v>
       </c>
       <c r="H7" t="n">
-        <v>103</v>
+        <v>102.84</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 20 / Fig 43 / Fig 45</t>
+          <t>CFPB 2025 Fig 50 / Fig 18 / Fig 85 / Fig 43 / Fig 45</t>
         </is>
       </c>
     </row>
@@ -687,6 +698,11 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -713,12 +729,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Figure 50 - Share of active accounts revolving, 2024</t>
+          <t>Figure 50 - Share of active accounts revolving, 2024 (Y-14+)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>General purpose cards. Deep y Subprime comparten 88%</t>
+          <t>General purpose cards. Datos exactos del Excel de figuras CFPB.</t>
         </is>
       </c>
     </row>
@@ -730,12 +746,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Figure 18 - Average per-account cycle-ending balances, year-end 2024</t>
+          <t>Figure 18 - Average per-account cycle-ending balances, year-end 2024 (CCIP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>General purpose cards. Deep subprime y subprime estimados de grafica Fig 18</t>
+          <t>General purpose cards. Datos exactos del Excel de figuras CFPB.</t>
         </is>
       </c>
     </row>
@@ -747,12 +763,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Figure 85 - Average APR on new accounts, general purpose, 2024</t>
+          <t>Figure 85 - Average APR on new accounts, general purpose (Y-14)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basado en Fig 85 rangos de score. Deep subprime = under 620</t>
+          <t>Fig 85 usa rangos de score que no coinciden exactamente con bandas FICO. Supuestos: Deep Subprime y Subprime = Under 620 (30.0%). Near-Prime = promedio 620-639 (29.85%) y 640-659 (29.42%) = 29.6%. Prime = promedio 660-679 (29.18%), 680-699 (28.97%), 700-719 (28.73%) = 28.96%. Prime Plus = promedio 720-739 (28.16%) y 740-759 (27.28%) = 27.72%. Superprime = 760+ (25.83%).</t>
         </is>
       </c>
     </row>
@@ -769,7 +785,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>General purpose revolving accounts. Fig 20</t>
+          <t>General purpose revolving accounts. No verificado en esta corrección, se mantiene valor original.</t>
         </is>
       </c>
     </row>
@@ -781,12 +797,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Figure 45 - Share of accounts making just the minimum payment due, 2024</t>
+          <t>Figure 45 - Share of accounts making just the minimum payment due, 2024 (Y-14+)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>General purpose cards. Fig 45</t>
+          <t>General purpose cards. Datos exactos del Excel de figuras CFPB.</t>
         </is>
       </c>
     </row>
@@ -798,12 +814,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Figure 43 - Payment rate, 2024</t>
+          <t>Figure 43 - Payment rate, 2024 (Y-14+)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>General purpose cards. Fig 43. Superprime &gt;100% posible por pagos extra</t>
+          <t>General purpose cards. Datos exactos del Excel de figuras CFPB. Superprime &gt;100% porque incluye pagos extra.</t>
         </is>
       </c>
     </row>
